--- a/BASE_ALERTAS_NACIONAL_2026_JOAO.xlsx
+++ b/BASE_ALERTAS_NACIONAL_2026_JOAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ServicioSocial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F46409-9385-466B-B1ED-CE8827EBFCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B8709-AAE3-4EAC-89D7-690CC5F1D5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="122">
   <si>
     <t>ID</t>
   </si>
@@ -71,6 +71,133 @@
     <t>AUTORIDAD QUE INGRESO EL REPORTE</t>
   </si>
   <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>FECHA
+ DE LOCALIZADO</t>
+  </si>
+  <si>
+    <t>AN/2846/2026</t>
+  </si>
+  <si>
+    <t>22-06-26</t>
+  </si>
+  <si>
+    <t>BRITANY YAZMIN PACHECO MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUJER</t>
+  </si>
+  <si>
+    <t>FEMENINO</t>
+  </si>
+  <si>
+    <t>MEXICANA</t>
+  </si>
+  <si>
+    <t>FI26-153F77633-83DB-47BA-8070-DC5FC16A0475</t>
+  </si>
+  <si>
+    <t>22-05-26</t>
+  </si>
+  <si>
+    <t>CIUDAD DE MEXICO</t>
+  </si>
+  <si>
+    <t>FISCALÍA GENERAL DE JUSTICIA DE LA CIUDAD DE MÉXICO</t>
+  </si>
+  <si>
+    <t>AN/2847/2026</t>
+  </si>
+  <si>
+    <t>GILBERTO OSUNA MORALES</t>
+  </si>
+  <si>
+    <t>HOMBRE</t>
+  </si>
+  <si>
+    <t>MASCULINO</t>
+  </si>
+  <si>
+    <t>FI26-10AD9BD19-6E58-4B08-98EA-9E1F5F0437C6</t>
+  </si>
+  <si>
+    <t>SONORA</t>
+  </si>
+  <si>
+    <t>FISCALIA GENERAL DE JUSTICIA DEL ESTADO DE SONORA</t>
+  </si>
+  <si>
+    <t>AN/2848/2026</t>
+  </si>
+  <si>
+    <t>VICTOR MILLAN BECERRA</t>
+  </si>
+  <si>
+    <t>FI26-112AB3067-BDFC-4E9D-AEDF-39CE4DAADCC6</t>
+  </si>
+  <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
+    <t>COMISION DE BUSQUEDA DE PERSONAS DEL ESTADO DE PUEBLA</t>
+  </si>
+  <si>
+    <t>AN/2849/2026</t>
+  </si>
+  <si>
+    <t>CALEB EMMANUEL LAGUNAS ESPINOZA</t>
+  </si>
+  <si>
+    <t>FI26-1C22E33CF-C5E1-4850-AB89-71C5A3210774</t>
+  </si>
+  <si>
+    <t>AN/2850/2026</t>
+  </si>
+  <si>
+    <t>AN/2851/2026</t>
+  </si>
+  <si>
+    <t>AN/2852/2026</t>
+  </si>
+  <si>
+    <t>AN/2853/2026</t>
+  </si>
+  <si>
+    <t>AN/2854/2026</t>
+  </si>
+  <si>
+    <t>AN/2855/2026</t>
+  </si>
+  <si>
+    <t>AN/2856/2026</t>
+  </si>
+  <si>
+    <t>AN/2857/2026</t>
+  </si>
+  <si>
+    <t>AN/2858/2026</t>
+  </si>
+  <si>
+    <t>AN/2859/2026</t>
+  </si>
+  <si>
+    <t>AN/2860/2026</t>
+  </si>
+  <si>
+    <t>AN/2961/2026</t>
+  </si>
+  <si>
+    <t>17-06-26</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>FISCALÍA GENERAL DE JUSTICIA DE LA CIUDAD DE MÉXICO.</t>
+  </si>
+  <si>
     <t>¿Habla español?</t>
   </si>
   <si>
@@ -102,57 +229,6 @@
   </si>
   <si>
     <t>Lugar de nacimiento</t>
-  </si>
-  <si>
-    <t>AN/2846/2026</t>
-  </si>
-  <si>
-    <t>22-06-26</t>
-  </si>
-  <si>
-    <t>BRITANY YAZMIN PACHECO MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUJER</t>
-  </si>
-  <si>
-    <t>FEMENINO</t>
-  </si>
-  <si>
-    <t>MEXICANA</t>
-  </si>
-  <si>
-    <t>FI26-153F77633-83DB-47BA-8070-DC5FC16A0475</t>
-  </si>
-  <si>
-    <t>22-05-26</t>
-  </si>
-  <si>
-    <t>CIUDAD DE MEXICO</t>
-  </si>
-  <si>
-    <t>FISCALÍA GENERAL DE JUSTICIA DE LA CIUDAD DE MÉXICO</t>
-  </si>
-  <si>
-    <t>AN/2847/2026</t>
-  </si>
-  <si>
-    <t>GILBERTO OSUNA MORALES</t>
-  </si>
-  <si>
-    <t>HOMBRE</t>
-  </si>
-  <si>
-    <t>MASCULINO</t>
-  </si>
-  <si>
-    <t>FI26-10AD9BD19-6E58-4B08-98EA-9E1F5F0437C6</t>
-  </si>
-  <si>
-    <t>SONORA</t>
-  </si>
-  <si>
-    <t>FISCALIA GENERAL DE JUSTICIA DEL ESTADO DE SONORA</t>
   </si>
   <si>
     <t>SI</t>
@@ -190,21 +266,6 @@
 TENIS COLOR: NEGRO/BLANCO</t>
   </si>
   <si>
-    <t>AN/2848/2026</t>
-  </si>
-  <si>
-    <t>VICTOR MILLAN BECERRA</t>
-  </si>
-  <si>
-    <t>FI26-112AB3067-BDFC-4E9D-AEDF-39CE4DAADCC6</t>
-  </si>
-  <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
-    <t>COMISION DE BUSQUEDA DE PERSONAS DEL ESTADO DE PUEBLA</t>
-  </si>
-  <si>
     <t>02:30</t>
   </si>
   <si>
@@ -220,15 +281,6 @@
     <t>NINGUNA</t>
   </si>
   <si>
-    <t>AN/2849/2026</t>
-  </si>
-  <si>
-    <t>CALEB EMMANUEL LAGUNAS ESPINOZA</t>
-  </si>
-  <si>
-    <t>FI26-1C22E33CF-C5E1-4850-AB89-71C5A3210774</t>
-  </si>
-  <si>
     <t>07:00</t>
   </si>
   <si>
@@ -247,9 +299,6 @@
     <t>CUATRO CICATRICES ARRIBA DE LA OREJA EN LA PARTE DERECHA</t>
   </si>
   <si>
-    <t>AN/2850/2026</t>
-  </si>
-  <si>
     <t>JOSE ANGEL SAMANIEGO</t>
   </si>
   <si>
@@ -274,9 +323,6 @@
     <t>CAMISETA, PANTALÓN</t>
   </si>
   <si>
-    <t>AN/2851/2026</t>
-  </si>
-  <si>
     <t>ALISON AISLINN DE SANTIAGO RAMIREZ</t>
   </si>
   <si>
@@ -304,9 +350,6 @@
     <t>TATUJE EN SU MANO IZQUIERDA DE UNA BALLENA , CICATRICES POR CORTADURAS EN AMBOS BRAZOS</t>
   </si>
   <si>
-    <t>AN/2852/2026</t>
-  </si>
-  <si>
     <t>RODIBERTO DE LA FLOR ARGUELLEZ</t>
   </si>
   <si>
@@ -334,9 +377,6 @@
     <t>TATUAJE EN EL ANTEBRAZO IZQUIERDO UN CORAZON.</t>
   </si>
   <si>
-    <t>AN/2853/2026</t>
-  </si>
-  <si>
     <t>OLIVER JOSUE RODRIGUEZ RUIZ</t>
   </si>
   <si>
@@ -359,39 +399,6 @@
   </si>
   <si>
     <t>CHAMARRA COLOR: NEGRO, PANTALÓN, PLAYERA COLOR: NEGRO, TENIS COLOR: NEGRO</t>
-  </si>
-  <si>
-    <t>AN/2854/2026</t>
-  </si>
-  <si>
-    <t>AN/2855/2026</t>
-  </si>
-  <si>
-    <t>AN/2856/2026</t>
-  </si>
-  <si>
-    <t>AN/2857/2026</t>
-  </si>
-  <si>
-    <t>AN/2858/2026</t>
-  </si>
-  <si>
-    <t>AN/2859/2026</t>
-  </si>
-  <si>
-    <t>AN/2860/2026</t>
-  </si>
-  <si>
-    <t>AN/2961/2026</t>
-  </si>
-  <si>
-    <t>17-06-26</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>FISCALÍA GENERAL DE JUSTICIA DE LA CIUDAD DE MÉXICO.</t>
   </si>
 </sst>
 </file>
@@ -430,7 +437,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,6 +460,18 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFA9D08E"/>
       </patternFill>
     </fill>
   </fills>
@@ -483,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -508,6 +527,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -842,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="3" customWidth="1"/>
@@ -859,11 +888,12 @@
     <col min="13" max="13" width="21.5546875" style="5" customWidth="1"/>
     <col min="14" max="14" width="58.6640625" style="5" customWidth="1"/>
     <col min="15" max="15" width="16.33203125" style="5" customWidth="1"/>
-    <col min="16" max="26" width="11.5546875" style="5" customWidth="1"/>
-    <col min="27" max="16384" width="11.5546875" style="5"/>
+    <col min="16" max="16" width="12.88671875" style="8" customWidth="1"/>
+    <col min="17" max="30" width="11.5546875" style="5" customWidth="1"/>
+    <col min="31" max="16384" width="11.5546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -906,19 +936,25 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>2846</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E2" s="5">
         <v>15</v>
@@ -927,398 +963,184 @@
         <v>15</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2847</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="5">
-        <v>56</v>
-      </c>
-      <c r="F3" s="5">
-        <v>56</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="8">
-        <v>46183</v>
-      </c>
-      <c r="L3" s="10">
-        <v>46184</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2848</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="5">
-        <v>21</v>
-      </c>
-      <c r="F4" s="5">
-        <v>21</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="8">
-        <v>46093</v>
-      </c>
-      <c r="L4" s="10">
-        <v>46192</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2849</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="5">
-        <v>43</v>
-      </c>
-      <c r="F5" s="5">
-        <v>43</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="B5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5" s="8">
-        <v>46192</v>
-      </c>
-      <c r="L5" s="10">
-        <v>46192</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C5" s="14"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2850</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="5">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5">
-        <v>22</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="8">
-        <v>46088</v>
-      </c>
-      <c r="L6" s="10">
-        <v>46088</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C6" s="10"/>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2851</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="5">
-        <v>36</v>
-      </c>
-      <c r="F7" s="5">
-        <v>36</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="8">
-        <v>46086</v>
-      </c>
-      <c r="L7" s="10">
-        <v>46086</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>2852</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="5">
-        <v>45</v>
-      </c>
-      <c r="F8" s="5">
-        <v>45</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="8">
-        <v>46172</v>
-      </c>
-      <c r="L8" s="10">
-        <v>46172</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>2853</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="10">
-        <v>46199</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="5">
-        <v>6</v>
-      </c>
-      <c r="F9" s="5">
-        <v>6</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="8">
-        <v>46192</v>
-      </c>
-      <c r="L9" s="10">
-        <v>46192</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="17"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2854</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="C10" s="10"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2855</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C11" s="10"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>2856</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C12" s="10"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>2857</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2858</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2859</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2860</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
@@ -1826,43 +1648,43 @@
         <v>2961</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y117"/>
+  <dimension ref="A1:AA117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="3" customWidth="1"/>
@@ -1901,11 +1723,11 @@
     <col min="24" max="24" width="38.109375" style="5" customWidth="1"/>
     <col min="25" max="25" width="26.88671875" style="5" customWidth="1"/>
     <col min="26" max="26" width="20.6640625" style="5" customWidth="1"/>
-    <col min="27" max="28" width="11.5546875" style="5" customWidth="1"/>
-    <col min="29" max="16384" width="11.5546875" style="5"/>
+    <col min="27" max="32" width="11.5546875" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="11.5546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="1" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1949,51 +1771,57 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>2846</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E2" s="5">
         <v>15</v>
@@ -2002,42 +1830,42 @@
         <v>15</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2847</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C3" s="10">
         <v>46205</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E3" s="5">
         <v>36</v>
@@ -2046,16 +1874,16 @@
         <v>36</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="K3" s="8">
         <v>46086</v>
@@ -2064,54 +1892,54 @@
         <v>46086</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2848</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C4" s="10">
         <v>46205</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E4" s="5">
         <v>45</v>
@@ -2120,16 +1948,16 @@
         <v>45</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K4" s="8">
         <v>46172</v>
@@ -2138,54 +1966,54 @@
         <v>46172</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2849</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C5" s="10">
         <v>46205</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5">
         <v>6</v>
@@ -2194,16 +2022,16 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="K5" s="8">
         <v>46192</v>
@@ -2212,54 +2040,54 @@
         <v>46192</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="U5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="V5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2850</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C6" s="10">
         <v>46205</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E6" s="5">
         <v>56</v>
@@ -2268,16 +2096,16 @@
         <v>56</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="K6" s="8">
         <v>46183</v>
@@ -2286,57 +2114,57 @@
         <v>46184</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="Y6" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2851</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="C7" s="10">
         <v>46205</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E7" s="5">
         <v>21</v>
@@ -2345,16 +2173,16 @@
         <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="K7" s="8">
         <v>46093</v>
@@ -2363,57 +2191,57 @@
         <v>46192</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>2852</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C8" s="10">
         <v>46205</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E8" s="5">
         <v>43</v>
@@ -2422,16 +2250,16 @@
         <v>43</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="K8" s="8">
         <v>46192</v>
@@ -2440,57 +2268,57 @@
         <v>46192</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>2853</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10">
         <v>46205</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E9" s="5">
         <v>21</v>
@@ -2499,16 +2327,16 @@
         <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>102</v>
+        <v>21</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="K9" s="8">
         <v>46088</v>
@@ -2517,105 +2345,105 @@
         <v>46088</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2854</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="C10" s="10"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2855</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="C11" s="10"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>2856</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C12" s="10"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>2857</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2858</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2859</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2860</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
@@ -3123,43 +2951,43 @@
         <v>2961</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
